--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484854_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484854_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8601</v>
+        <v>2.2145</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2792</v>
+        <v>0.2869</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1393</v>
+        <v>1.9277</v>
       </c>
       <c r="G2" t="n">
         <v>4.4325</v>
@@ -610,13 +610,13 @@
         <v>1.3209</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8242</v>
+        <v>1.1786</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5262</v>
+        <v>0.0399</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3504</v>
+        <v>1.1387</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. IBAÑEZ TEJERO</t>
+          <t>I. BARBERO LOPEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2678</v>
+        <v>1.8282</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2678</v>
+        <v>0.3086</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.5196</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2678</v>
+        <v>1.1105</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2678</v>
+        <v>0.2207</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.8898</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2678</v>
+        <v>1.5724</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2678</v>
+        <v>0.8561</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0.4619</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0.6354</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.1736</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.0192</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.5096</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.2839</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.5102</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.9434</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. BARBERO LOPEZ</t>
+          <t>J. IBAÑEZ TEJERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2621</v>
+        <v>1.2678</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2575</v>
+        <v>1.2678</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5196</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1105</v>
+        <v>1.2678</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2207</v>
+        <v>1.2678</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8898</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5724</v>
+        <v>1.2678</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8561</v>
+        <v>1.2678</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7161999999999999</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4619</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6354</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1736</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5096</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0192</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5096</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7178</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0559</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7737000000000001</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9434</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. NAKIDJIM</t>
+          <t>J. SANTONJA FERRERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4473</v>
+        <v>0.2837</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.278</v>
+        <v>0.7405</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8307</v>
+        <v>-0.4568</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.3465</v>
+        <v>-1.3463</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.2321</v>
+        <v>3.0114</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1143</v>
+        <v>-4.3578</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.2949</v>
+        <v>1.2706</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.4183</v>
+        <v>4.395</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1234</v>
+        <v>-3.1244</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0516</v>
+        <v>-2.617</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8139</v>
+        <v>-1.3836</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2377</v>
+        <v>-1.2334</v>
       </c>
       <c r="P6" t="n">
-        <v>-4.5288</v>
+        <v>0.3774</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.8497</v>
+        <v>-1.1322</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="S6" t="n">
-        <v>4.6358</v>
+        <v>0.9319</v>
       </c>
       <c r="T6" t="n">
-        <v>3.0743</v>
+        <v>-0.0205</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5614</v>
+        <v>0.9524</v>
       </c>
       <c r="V6" t="n">
-        <v>2.7922</v>
+        <v>0.3208</v>
       </c>
       <c r="W6" t="n">
-        <v>2.7922</v>
+        <v>0.6226</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5447</v>
+        <v>-0.4006</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3645</v>
+        <v>-0.2469</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1802</v>
+        <v>-0.1537</v>
       </c>
       <c r="G7" t="n">
         <v>-1.489</v>
@@ -1000,13 +1000,13 @@
         <v>0.1887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6425</v>
+        <v>0.7866</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0029</v>
+        <v>0.1205</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.6661</v>
       </c>
       <c r="V7" t="n">
         <v>0.3018</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SANTONJA FERRERO</t>
+          <t>A. VILAGRAN GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9715</v>
+        <v>-1.163</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1179</v>
+        <v>-0.624</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8536</v>
+        <v>-0.539</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3463</v>
+        <v>-1.6819</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0114</v>
+        <v>-0.2293</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.3578</v>
+        <v>-1.4526</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2706</v>
+        <v>-0.545</v>
       </c>
       <c r="K8" t="n">
-        <v>4.395</v>
+        <v>0.0634</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.1244</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.617</v>
+        <v>-1.1369</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3836</v>
+        <v>-0.2927</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2334</v>
+        <v>-0.8442</v>
       </c>
       <c r="P8" t="n">
         <v>0.3774</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5096</v>
+        <v>0.3774</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3233</v>
+        <v>0.1415</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8789</v>
+        <v>-0.0789</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5556</v>
+        <v>0.2205</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VILAGRAN GONZALEZ</t>
+          <t>A. VALDERRAMA CARRENO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.181</v>
+        <v>-1.9045</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7214</v>
+        <v>-1.7745</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4596</v>
+        <v>-0.13</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6819</v>
+        <v>-2.6958</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2293</v>
+        <v>-0.9422</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4526</v>
+        <v>-1.7535</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.545</v>
+        <v>-1.5417</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0634</v>
+        <v>-0.2426</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-1.2991</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1369</v>
+        <v>-1.1541</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2927</v>
+        <v>-0.6996</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8442</v>
+        <v>-0.4544</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3774</v>
+        <v>0.5661</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3774</v>
+        <v>0.7548</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1235</v>
+        <v>0.546</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1764</v>
+        <v>0.2767</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2998</v>
+        <v>0.2693</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA CARRENO</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1078</v>
+        <v>-2.4096</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.872</v>
+        <v>-2.1927</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2358</v>
+        <v>-0.2169</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6958</v>
+        <v>-1.6999</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9422</v>
+        <v>-1.4165</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7535</v>
+        <v>-0.2834</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5417</v>
+        <v>-0.513</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2426</v>
+        <v>-0.5541</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2991</v>
+        <v>0.0411</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1541</v>
+        <v>-1.1869</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6996</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4544</v>
+        <v>-0.3245</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5661</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1887</v>
+        <v>-1.887</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7548</v>
+        <v>0.1887</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3427</v>
+        <v>0.6868</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1793</v>
+        <v>-0.0945</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1634</v>
+        <v>0.7813</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3208</v>
+        <v>0.3018</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3208</v>
+        <v>0.3018</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>N. RAMOS CAMPOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1535</v>
+        <v>-2.762</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0953</v>
+        <v>-0.8184</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0582</v>
+        <v>-1.9436</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6999</v>
+        <v>-2.4944</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4165</v>
+        <v>-0.0266</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2834</v>
+        <v>-2.4678</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.513</v>
+        <v>-0.2692</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5541</v>
+        <v>0.3803</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0411</v>
+        <v>-0.6496</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1869</v>
+        <v>-2.2252</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-0.4069</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3245</v>
+        <v>-1.8182</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6983</v>
+        <v>0.1887</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0.1887</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9429</v>
+        <v>-0.4563</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0029</v>
+        <v>-0.5492</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.0929</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. RAMOS CAMPOS</t>
+          <t>P. NAKIDJIM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1299</v>
+        <v>-2.899</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9747</v>
+        <v>-4.1478</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1552</v>
+        <v>1.2487</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4944</v>
+        <v>-3.3465</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0266</v>
+        <v>-3.2321</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.4678</v>
+        <v>-0.1143</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2692</v>
+        <v>-2.2949</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3803</v>
+        <v>-2.4183</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6496</v>
+        <v>0.1234</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.2252</v>
+        <v>-1.0516</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4069</v>
+        <v>-0.8139</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8182</v>
+        <v>-0.2377</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1887</v>
+        <v>-4.5288</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-5.8497</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1887</v>
+        <v>1.3209</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8242</v>
+        <v>2.184</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7055</v>
+        <v>1.2046</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1187</v>
+        <v>0.9794</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>2.7922</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.7922</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.0286</v>
+        <v>-3.6834</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.918</v>
+        <v>-2.6257</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1106</v>
+        <v>-1.0577</v>
       </c>
       <c r="G13" t="n">
         <v>-1.552</v>
@@ -1468,13 +1468,13 @@
         <v>0.5661</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2122</v>
+        <v>0.133</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1764</v>
+        <v>0.1159</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0359</v>
+        <v>0.0171</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.3234</v>
+        <v>-5.9879</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.8649</v>
+        <v>-5.7674</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4586</v>
+        <v>-0.2205</v>
       </c>
       <c r="G14" t="n">
         <v>-6.3305</v>
@@ -1546,13 +1546,13 @@
         <v>0.5661</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3844</v>
+        <v>0.72</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2323</v>
+        <v>-0.1348</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6167</v>
+        <v>0.8548</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,28 +1579,28 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-16.1807</v>
+        <v>-15.2988</v>
       </c>
       <c r="E15" t="n">
-        <v>-16.1586</v>
+        <v>-15.2766</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.02219999999999989</v>
+        <v>-0.02220000000000008</v>
       </c>
       <c r="G15" t="n">
         <v>-15.5085</v>
       </c>
       <c r="H15" t="n">
-        <v>-6.417300000000001</v>
+        <v>-6.417299999999999</v>
       </c>
       <c r="I15" t="n">
         <v>-9.091099999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8522999999999987</v>
+        <v>-0.8522999999999983</v>
       </c>
       <c r="K15" t="n">
-        <v>1.963999999999999</v>
+        <v>1.964</v>
       </c>
       <c r="L15" t="n">
         <v>-2.8166</v>
@@ -1609,7 +1609,7 @@
         <v>-14.6562</v>
       </c>
       <c r="N15" t="n">
-        <v>-8.3813</v>
+        <v>-8.381300000000001</v>
       </c>
       <c r="O15" t="n">
         <v>-6.2747</v>
@@ -1618,19 +1618,19 @@
         <v>-12.2655</v>
       </c>
       <c r="Q15" t="n">
-        <v>-20.757</v>
+        <v>-20.75700000000001</v>
       </c>
       <c r="R15" t="n">
         <v>8.4915</v>
       </c>
       <c r="S15" t="n">
-        <v>7.254099999999999</v>
+        <v>8.136000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5077999999999998</v>
+        <v>1.3899</v>
       </c>
       <c r="U15" t="n">
-        <v>6.746000000000001</v>
+        <v>6.7462</v>
       </c>
       <c r="V15" t="n">
         <v>4.3392</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.6143</v>
+        <v>8.9415</v>
       </c>
       <c r="E16" t="n">
-        <v>5.8292</v>
+        <v>6.0241</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7851</v>
+        <v>2.9174</v>
       </c>
       <c r="G16" t="n">
         <v>8.1364</v>
@@ -1702,13 +1702,13 @@
         <v>2.2644</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.843</v>
+        <v>-0.5158</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7642</v>
+        <v>-0.5694</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.0535</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6436</v>
+        <v>4.2185</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6175</v>
+        <v>2.0073</v>
       </c>
       <c r="F17" t="n">
-        <v>2.026</v>
+        <v>2.2112</v>
       </c>
       <c r="G17" t="n">
         <v>3.8929</v>
@@ -1780,13 +1780,13 @@
         <v>2.0757</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0799</v>
+        <v>-0.505</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9994</v>
+        <v>-0.6097</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0805</v>
+        <v>0.1047</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2452</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MARZIALI</t>
+          <t>J. ORTOLA TOMAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3772</v>
+        <v>3.4563</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8736</v>
+        <v>1.365</v>
       </c>
       <c r="F18" t="n">
-        <v>4.2509</v>
+        <v>2.0913</v>
       </c>
       <c r="G18" t="n">
-        <v>2.349</v>
+        <v>3.182</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7687</v>
+        <v>0.6926</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5803</v>
+        <v>2.4894</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0098</v>
+        <v>1.9545</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7545</v>
+        <v>0.6128</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2553</v>
+        <v>1.3417</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3392</v>
+        <v>1.2275</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0141</v>
+        <v>0.0798</v>
       </c>
       <c r="O18" t="n">
-        <v>0.325</v>
+        <v>1.1476</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1322</v>
+        <v>2.2644</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.0192</v>
+        <v>2.2644</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.104</v>
+        <v>-0.4431</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9965000000000001</v>
+        <v>-0.5895</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8925</v>
+        <v>0.1464</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ORTOLA TOMAS</t>
+          <t>S. JIMENA LLORCA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.0317</v>
+        <v>2.881</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0727</v>
+        <v>1.9094</v>
       </c>
       <c r="F19" t="n">
-        <v>1.959</v>
+        <v>0.9716</v>
       </c>
       <c r="G19" t="n">
-        <v>3.182</v>
+        <v>3.0055</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6926</v>
+        <v>1.2866</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4894</v>
+        <v>1.7189</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9545</v>
+        <v>3.1747</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6128</v>
+        <v>1.1097</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3417</v>
+        <v>2.065</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2275</v>
+        <v>-0.1692</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0798</v>
+        <v>0.1769</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1476</v>
+        <v>-0.3461</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2644</v>
+        <v>1.3209</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R19" t="n">
         <v>2.2644</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8677</v>
+        <v>-0.8228</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8818</v>
+        <v>-0.6236</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0142</v>
+        <v>-0.1992</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.547</v>
+        <v>-0.6226</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.547</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. JIMENA LLORCA</t>
+          <t>T. DESPLACE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.8197</v>
+        <v>2.5924</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0068</v>
+        <v>1.1709</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8129</v>
+        <v>1.4215</v>
       </c>
       <c r="G20" t="n">
-        <v>3.0055</v>
+        <v>1.6489</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2866</v>
+        <v>1.1488</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7189</v>
+        <v>0.5001</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1747</v>
+        <v>1.8176</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1097</v>
+        <v>1.6857</v>
       </c>
       <c r="L20" t="n">
-        <v>2.065</v>
+        <v>0.1319</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1692</v>
+        <v>-0.1687</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1769</v>
+        <v>-0.5369</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3461</v>
+        <v>0.3682</v>
       </c>
       <c r="P20" t="n">
         <v>1.3209</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2644</v>
+        <v>1.3209</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8841</v>
+        <v>-0.3774</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5262</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3579</v>
+        <v>0.2693</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. DESPLACE</t>
+          <t>M. MARZIALI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.804</v>
+        <v>2.3623</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1709</v>
+        <v>-1.0685</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6331</v>
+        <v>3.4308</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6489</v>
+        <v>2.349</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1488</v>
+        <v>1.7687</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5001</v>
+        <v>0.5803</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8176</v>
+        <v>2.0098</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6857</v>
+        <v>1.7545</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1319</v>
+        <v>0.2553</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1687</v>
+        <v>0.3392</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5369</v>
+        <v>0.0141</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3682</v>
+        <v>0.325</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3209</v>
+        <v>1.1322</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3209</v>
+        <v>3.0192</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1658</v>
+        <v>-1.119</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-1.1914</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4809</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4718</v>
+        <v>1.6485</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0009</v>
+        <v>0.0983</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4709</v>
+        <v>1.5502</v>
       </c>
       <c r="G22" t="n">
         <v>1.0291</v>
@@ -2170,13 +2170,13 @@
         <v>1.1322</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6896</v>
+        <v>-0.5128</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4115</v>
+        <v>-0.3141</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.278</v>
+        <v>-0.1987</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5561</v>
+        <v>-2.3105</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2181</v>
+        <v>-3.2899</v>
       </c>
       <c r="F23" t="n">
-        <v>0.662</v>
+        <v>0.9794</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2142</v>
@@ -2248,13 +2248,13 @@
         <v>3.0192</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1723</v>
+        <v>-0.9266</v>
       </c>
       <c r="T23" t="n">
-        <v>0.479</v>
+        <v>-0.5928</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6513</v>
+        <v>-0.3338</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3018</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9698</v>
+        <v>-3.6872</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.258</v>
+        <v>-3.1605</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7119</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4241</v>
@@ -2326,13 +2326,13 @@
         <v>0.5661</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8665</v>
+        <v>-0.5839</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4703</v>
+        <v>-0.3729</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3962</v>
+        <v>-0.211</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3018</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0556</v>
+        <v>-3.922</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.3262</v>
+        <v>-5.0339</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2706</v>
+        <v>1.1119</v>
       </c>
       <c r="G25" t="n">
         <v>-3.097</v>
@@ -2404,13 +2404,13 @@
         <v>2.8305</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5813</v>
+        <v>-1.4477</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.5285</v>
+        <v>-1.2362</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0528</v>
+        <v>-0.2116</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3208</v>
@@ -2440,7 +2440,7 @@
         <v>16.1808</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02209999999999912</v>
+        <v>0.02219999999999978</v>
       </c>
       <c r="F26" t="n">
         <v>16.1586</v>
@@ -2449,7 +2449,7 @@
         <v>15.5085</v>
       </c>
       <c r="H26" t="n">
-        <v>6.417299999999999</v>
+        <v>6.417300000000001</v>
       </c>
       <c r="I26" t="n">
         <v>9.091099999999997</v>
@@ -2482,16 +2482,16 @@
         <v>20.757</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.2542</v>
+        <v>-7.2541</v>
       </c>
       <c r="T26" t="n">
-        <v>-6.746099999999999</v>
+        <v>-6.7463</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5078</v>
+        <v>-0.508</v>
       </c>
       <c r="V26" t="n">
-        <v>-4.339200000000001</v>
+        <v>-4.3392</v>
       </c>
       <c r="W26" t="n">
         <v>0.6036</v>
